--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484871_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484871_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.8506</v>
+        <v>9.295</v>
       </c>
       <c r="E2" t="n">
         <v>7.9152</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9354</v>
+        <v>1.3798</v>
       </c>
       <c r="G2" t="n">
         <v>6.3565</v>
@@ -610,13 +610,13 @@
         <v>1.887</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0035</v>
+        <v>0.448</v>
       </c>
       <c r="T2" t="n">
         <v>-0.1023</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1059</v>
+        <v>0.5503</v>
       </c>
       <c r="V2" t="n">
         <v>1.547</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8157</v>
+        <v>6.1655</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6031</v>
+        <v>3.6619</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2126</v>
+        <v>2.5036</v>
       </c>
       <c r="G3" t="n">
         <v>4.3991</v>
@@ -688,13 +688,13 @@
         <v>1.6983</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0394</v>
+        <v>0.3892</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1328</v>
+        <v>0.1916</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0934</v>
+        <v>0.1976</v>
       </c>
       <c r="V3" t="n">
         <v>2.5094</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.6655</v>
+        <v>6.0598</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1195</v>
+        <v>2.2757</v>
       </c>
       <c r="F4" t="n">
-        <v>3.546</v>
+        <v>3.7841</v>
       </c>
       <c r="G4" t="n">
         <v>2.9484</v>
@@ -766,13 +766,13 @@
         <v>2.6418</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.4696</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2039</v>
+        <v>0.3602</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1287</v>
+        <v>0.1094</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3121</v>
+        <v>3.389</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5378</v>
+        <v>2.694</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7743</v>
+        <v>0.6949</v>
       </c>
       <c r="G5" t="n">
         <v>2.892</v>
@@ -844,13 +844,13 @@
         <v>2.2644</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0618</v>
+        <v>0.1386</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.09</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1518</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0.9244</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. CAZORLA ZARAGOZI</t>
+          <t>S. GOMEZ VELEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1376</v>
+        <v>-0.8627</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1891</v>
+        <v>-1.6151</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3267</v>
+        <v>0.7524</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3951</v>
+        <v>-1.3835</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4969</v>
+        <v>0.4242</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1018</v>
+        <v>-1.8077</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1638</v>
+        <v>-0.6516</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1057</v>
+        <v>0.5071</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0582</v>
+        <v>-1.1587</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5589</v>
+        <v>-0.732</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6026</v>
+        <v>-0.0829</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0437</v>
+        <v>-0.649</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9435</v>
+        <v>1.887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0823</v>
+        <v>-0.7245</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7236</v>
+        <v>-0.3219</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8058999999999999</v>
+        <v>-0.4026</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3398</v>
+        <v>0.3018</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2452</v>
+        <v>0.3018</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.9054</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. MARZIALI</t>
+          <t>D. CAZORLA ZARAGOZI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1092</v>
+        <v>-0.8642</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0151</v>
+        <v>0.4096</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1242</v>
+        <v>-1.2738</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8618</v>
+        <v>-0.3951</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2835</v>
+        <v>-0.4969</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5783</v>
+        <v>0.1018</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6277</v>
+        <v>0.1638</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4478</v>
+        <v>0.1057</v>
       </c>
       <c r="L7" t="n">
-        <v>2.1799</v>
+        <v>0.0582</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7659</v>
+        <v>-0.5589</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1643</v>
+        <v>-0.6026</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6015</v>
+        <v>0.0437</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.7175</v>
+        <v>-0.9435</v>
       </c>
       <c r="R7" t="n">
-        <v>1.887</v>
+        <v>0.9435</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1993</v>
+        <v>-0.8089</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1023</v>
+        <v>-0.0559</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3016</v>
+        <v>-0.753</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3398</v>
+        <v>0.3398</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2072</v>
+        <v>1.2452</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.547</v>
+        <v>-0.9054</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. GOMEZ VELEZ</t>
+          <t>M. MARZIALI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3016</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8688</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5672</v>
+        <v>-1.0713</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3835</v>
+        <v>1.8618</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4242</v>
+        <v>1.2835</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.8077</v>
+        <v>0.5783</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6516</v>
+        <v>3.6277</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5071</v>
+        <v>1.4478</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.1587</v>
+        <v>2.1799</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.732</v>
+        <v>-1.7659</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0829</v>
+        <v>-0.1643</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.649</v>
+        <v>-1.6015</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9435</v>
+        <v>-4.7175</v>
       </c>
       <c r="R8" t="n">
         <v>1.887</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1633</v>
+        <v>0.311</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5755</v>
+        <v>-0.0436</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5878</v>
+        <v>0.3545</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3018</v>
+        <v>-0.3398</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3018</v>
+        <v>1.2072</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4799</v>
+        <v>-3.3561</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4467</v>
+        <v>-2.3492</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0333</v>
+        <v>-1.0068</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0198</v>
@@ -1156,13 +1156,13 @@
         <v>0.3774</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9505</v>
+        <v>-0.8266</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3527</v>
+        <v>-0.2553</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5978</v>
+        <v>-0.5714</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9815</v>
+        <v>-3.9009</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3174</v>
+        <v>-4.0251</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3359</v>
+        <v>0.1242</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2613</v>
@@ -1234,13 +1234,13 @@
         <v>1.5096</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8522999999999999</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.458</v>
+        <v>-0.1657</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3944</v>
+        <v>-0.606</v>
       </c>
       <c r="V10" t="n">
         <v>-1.547</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>14.6341</v>
+        <v>14.9279</v>
       </c>
       <c r="E11" t="n">
-        <v>8.7469</v>
+        <v>9.040899999999997</v>
       </c>
       <c r="F11" t="n">
-        <v>5.887199999999999</v>
+        <v>5.887100000000001</v>
       </c>
       <c r="G11" t="n">
         <v>15.3981</v>
@@ -1312,13 +1312,13 @@
         <v>15.096</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6691</v>
+        <v>-1.3753</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-0.3267</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0487</v>
+        <v>-1.0488</v>
       </c>
       <c r="V11" t="n">
         <v>3.735600000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.0926</v>
+        <v>4.5729</v>
       </c>
       <c r="E12" t="n">
-        <v>4.6803</v>
+        <v>3.9008</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4123</v>
+        <v>0.6721</v>
       </c>
       <c r="G12" t="n">
         <v>1.9871</v>
@@ -1390,13 +1390,13 @@
         <v>2.2644</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7847</v>
+        <v>1.265</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4936</v>
+        <v>0.7141</v>
       </c>
       <c r="U12" t="n">
-        <v>0.291</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0.9434</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.816</v>
+        <v>2.9194</v>
       </c>
       <c r="E13" t="n">
         <v>2.2359</v>
       </c>
       <c r="F13" t="n">
-        <v>0.58</v>
+        <v>0.6835</v>
       </c>
       <c r="G13" t="n">
         <v>0.5276999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>1.887</v>
       </c>
       <c r="S13" t="n">
-        <v>0.703</v>
+        <v>0.8065</v>
       </c>
       <c r="T13" t="n">
         <v>0.4296</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2734</v>
+        <v>0.3769</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3018</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. GARCIA CORBI</t>
+          <t>A. VAICIUNAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8777</v>
+        <v>2.3127</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9577</v>
+        <v>1.3071</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.08</v>
+        <v>1.0056</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5238</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0391</v>
+        <v>0.1174</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5629</v>
+        <v>-0.7358</v>
       </c>
       <c r="J14" t="n">
-        <v>2.0165</v>
+        <v>1.9166</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0423</v>
+        <v>1.7436</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9742</v>
+        <v>0.173</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4927</v>
+        <v>-2.5351</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0814</v>
+        <v>-1.6262</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4113</v>
+        <v>-0.9089</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3774</v>
+        <v>2.0757</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3774</v>
+        <v>3.0192</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0235</v>
+        <v>0.5536</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0588</v>
+        <v>0.0321</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0353</v>
+        <v>0.5215</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. VAICIUNAS</t>
+          <t>J. GARCIA CORBI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7244</v>
+        <v>2.028</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8199</v>
+        <v>2.0551</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9045</v>
+        <v>-0.0271</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6183999999999999</v>
+        <v>1.5238</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1174</v>
+        <v>-0.0391</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7358</v>
+        <v>1.5629</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9166</v>
+        <v>2.0165</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7436</v>
+        <v>0.0423</v>
       </c>
       <c r="L15" t="n">
-        <v>0.173</v>
+        <v>1.9742</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5351</v>
+        <v>-0.4927</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6262</v>
+        <v>-0.0814</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9089</v>
+        <v>-0.4113</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0757</v>
+        <v>0.3774</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.0192</v>
+        <v>0.3774</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0347</v>
+        <v>0.1268</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4551</v>
+        <v>0.0386</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4204</v>
+        <v>0.0882</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7262</v>
+        <v>-0.7393</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.0186</v>
+        <v>-1.9212</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2924</v>
+        <v>1.1818</v>
       </c>
       <c r="G16" t="n">
         <v>-3.1922</v>
@@ -1702,13 +1702,13 @@
         <v>2.8305</v>
       </c>
       <c r="S16" t="n">
-        <v>0.579</v>
+        <v>0.5659</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.053</v>
+        <v>0.0444</v>
       </c>
       <c r="U16" t="n">
-        <v>0.632</v>
+        <v>0.5215</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. BUHORSKYI</t>
+          <t>J. CALERO SEVILLANO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.212</v>
+        <v>-1.676</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-2.9257</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.1443</v>
+        <v>1.2496</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.622</v>
+        <v>-1.1222</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7497</v>
+        <v>-2.0355</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8723</v>
+        <v>0.9134</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2032</v>
+        <v>0.1348</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0798</v>
+        <v>-1.1246</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1234</v>
+        <v>1.2595</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8252</v>
+        <v>-1.257</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8295</v>
+        <v>-0.9109</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9956</v>
+        <v>-0.3461</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5661</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.887</v>
+        <v>-3.774</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3209</v>
+        <v>2.2644</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9005</v>
+        <v>0.3331</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3144</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4138</v>
+        <v>0.2422</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9244</v>
+        <v>0.6226</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3018</v>
+        <v>0.6226</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. CALERO SEVILLANO</t>
+          <t>D. BUHORSKYI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3196</v>
+        <v>-3.2225</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.4128</v>
+        <v>-1.2368</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0933</v>
+        <v>-1.9856</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1222</v>
+        <v>-1.622</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.0355</v>
+        <v>-0.7497</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9134</v>
+        <v>-0.8723</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1348</v>
+        <v>0.2032</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.1246</v>
+        <v>0.0798</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2595</v>
+        <v>0.1234</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.257</v>
+        <v>-1.8252</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9109</v>
+        <v>-0.8295</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3461</v>
+        <v>-0.9956</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5096</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.774</v>
+        <v>-1.887</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2644</v>
+        <v>1.3209</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3104</v>
+        <v>-0.11</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3963</v>
+        <v>0.1451</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0859</v>
+        <v>-0.2551</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6226</v>
+        <v>-0.9244</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6226</v>
+        <v>0.3018</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2262</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.6077</v>
+        <v>-5.236</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3925</v>
+        <v>-1.1002</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.2152</v>
+        <v>-4.1358</v>
       </c>
       <c r="G19" t="n">
         <v>-2.9054</v>
@@ -1936,13 +1936,13 @@
         <v>1.3209</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2875</v>
+        <v>0.0842</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2076</v>
+        <v>0.0847</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0799</v>
+        <v>-0.0005</v>
       </c>
       <c r="V19" t="n">
         <v>-2.7922</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.2411</v>
+        <v>-5.2644</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.6227</v>
+        <v>-4.0381</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6184</v>
+        <v>-1.2263</v>
       </c>
       <c r="G20" t="n">
         <v>-4.814</v>
@@ -2014,13 +2014,13 @@
         <v>2.0757</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.8794</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.281</v>
+        <v>-0.6964</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5984</v>
+        <v>-0.2063</v>
       </c>
       <c r="V20" t="n">
         <v>2.1506</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-9.0381</v>
+        <v>-9.0297</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.0667</v>
+        <v>-4.1641</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.9714</v>
+        <v>-4.8656</v>
       </c>
       <c r="G21" t="n">
         <v>-5.1626</v>
@@ -2092,13 +2092,13 @@
         <v>0.5661</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2375</v>
+        <v>0.2459</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2627</v>
+        <v>0.1653</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0253</v>
+        <v>0.0806</v>
       </c>
       <c r="V21" t="n">
         <v>-3.7356</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-14.634</v>
+        <v>-13.3349</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.887100000000001</v>
+        <v>-5.887200000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-8.7468</v>
+        <v>-7.447799999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-15.3982</v>
@@ -2140,7 +2140,7 @@
         <v>-7.387799999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-8.010399999999999</v>
+        <v>-8.010400000000001</v>
       </c>
       <c r="J22" t="n">
         <v>2.934500000000002</v>
@@ -2170,16 +2170,16 @@
         <v>17.9265</v>
       </c>
       <c r="S22" t="n">
-        <v>1.6692</v>
+        <v>2.9683</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0485</v>
+        <v>1.0484</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6205999999999999</v>
+        <v>1.9199</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.7356</v>
+        <v>-3.735599999999999</v>
       </c>
       <c r="W22" t="n">
         <v>5.2256</v>
